--- a/outputs/etf_trend_strategy/threshold_0.7/backtests/window_40/return_vol/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.7/backtests/window_40/return_vol/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -466,12 +466,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1367280640471411</v>
+        <v>-0.06312219655240103</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3096084607386864</v>
+        <v>0.1748519609326993</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.5743808737204795</v>
+        <v>-0.4191389181351402</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.8127633384214614</v>
+        <v>-0.559241442093841</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2518602171191403</v>
+        <v>0.1853656190055859</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.6187211923799237</v>
+        <v>-0.3832027880694936</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>40.9204790057202</v>
+        <v>36.01874691720026</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2447444722618559</v>
+        <v>-0.00686634668236441</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.252989526261686</v>
+        <v>0.2911253409245916</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.08700565385243</v>
+        <v>0.06880750536743205</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.410458549005768</v>
+        <v>0.1003288722627557</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3022050091063541</v>
+        <v>0.1874394050037237</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8386829057914073</v>
+        <v>-0.03814066431207992</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>53.36943323924685</v>
+        <v>24.90911306642192</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.01130258406161389</v>
+        <v>-0.09754582507439957</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2199989243183753</v>
+        <v>0.2282050311477072</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.01239409999747001</v>
+        <v>-0.4198399977770718</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.01890358655860604</v>
+        <v>-0.5858989077895724</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2305654667513349</v>
+        <v>0.2878127817203773</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.05103485216533116</v>
+        <v>-0.3521915187446271</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>59.38580293285121</v>
+        <v>62.46456764096305</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.1238790273617065</v>
+        <v>-0.1474760204341523</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2331635057525533</v>
+        <v>0.272143704624679</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.5383921341380444</v>
+        <v>-0.5293829862273765</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.7636917029250715</v>
+        <v>-0.7210354118779309</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2541746763514811</v>
+        <v>0.2172130336935381</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.5061633304101693</v>
+        <v>-0.7047382812309165</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>54.72498902389332</v>
+        <v>61.34069578747116</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.06559879720027229</v>
+        <v>0.07421504292028014</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2503865397881238</v>
+        <v>0.2699991694310802</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.3293307467046411</v>
+        <v>0.3548869674580581</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4520567142702796</v>
+        <v>0.5016280749070412</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2444212038755751</v>
+        <v>0.2276082091887482</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.278655596954303</v>
+        <v>0.3385953957949763</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>64.30026737077469</v>
+        <v>67.47345593718752</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.07531191691345374</v>
+        <v>0.4051394695809438</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3263612218858158</v>
+        <v>0.3804322552731742</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.5205589126029315</v>
+        <v>1.772004735776938</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.7299191392277711</v>
+        <v>2.758355401121344</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2100821336596655</v>
+        <v>0.1527318851487052</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.6697248568145359</v>
+        <v>5.583064123525844</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>43.52263800129927</v>
+        <v>39.94082073279323</v>
       </c>
     </row>
   </sheetData>
